--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513668_FASEFINALBFFB4_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513668_FASEFINALBFFB4_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. CHACON RODRIGUEZ</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3019</v>
+        <v>3.0277</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7189</v>
+        <v>2.5258</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.417</v>
+        <v>0.5019</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9512</v>
+        <v>1.8143</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8463</v>
+        <v>0.9811</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8952</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6392</v>
+        <v>2.9812</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5581</v>
+        <v>1.7166</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08110000000000001</v>
+        <v>1.2647</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.688</v>
+        <v>-1.167</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7118</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9762</v>
+        <v>-0.4315</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9737</v>
+        <v>-2.921</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9737</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5192</v>
+        <v>0.6066</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9423</v>
+        <v>0.6341</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4232</v>
+        <v>-0.0275</v>
       </c>
       <c r="V2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.8316</v>
       </c>
-      <c r="W2" t="n">
-        <v>2.1111</v>
-      </c>
       <c r="X2" t="n">
-        <v>-0.2795</v>
+        <v>0.1384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>I. CHACON RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5045</v>
+        <v>2.9666</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3643</v>
+        <v>4.2445</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1401</v>
+        <v>-1.2779</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8143</v>
+        <v>0.9512</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9811</v>
+        <v>1.8463</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8332000000000001</v>
+        <v>-0.8952</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9812</v>
+        <v>2.6392</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7166</v>
+        <v>2.5581</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2647</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.167</v>
+        <v>-1.688</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.7118</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4315</v>
+        <v>-0.9762</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3632</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.921</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5579</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0833</v>
+        <v>0.1839</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4726</v>
+        <v>0.4679</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3892</v>
+        <v>-0.284</v>
       </c>
       <c r="V3" t="n">
-        <v>1.97</v>
+        <v>1.8316</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8316</v>
+        <v>2.1111</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1384</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8137</v>
+        <v>1.6644</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.3723</v>
+        <v>1.0322</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1859</v>
+        <v>0.6323</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7072</v>
+        <v>1.6274</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8144</v>
+        <v>0.3079</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8927</v>
+        <v>1.3195</v>
       </c>
       <c r="J4" t="n">
-        <v>0.753</v>
+        <v>1.2049</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6314</v>
+        <v>0.0052</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1216</v>
+        <v>1.1997</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9542</v>
+        <v>0.4225</v>
       </c>
       <c r="N4" t="n">
-        <v>0.183</v>
+        <v>0.3027</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7712</v>
+        <v>0.1198</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3368</v>
+        <v>0.3895</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0895</v>
+        <v>-0.1947</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7526</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7391</v>
+        <v>-1.0145</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6779</v>
+        <v>-0.2575</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0612</v>
+        <v>-0.757</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2958</v>
+        <v>0.6621</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7137</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4179</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3932</v>
+        <v>0.4596</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7331</v>
+        <v>-2.5855</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6601</v>
+        <v>3.0451</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6274</v>
+        <v>1.7072</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3079</v>
+        <v>0.8144</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3195</v>
+        <v>0.8927</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2049</v>
+        <v>0.753</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0052</v>
+        <v>0.6314</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1997</v>
+        <v>0.1216</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4225</v>
+        <v>0.9542</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3027</v>
+        <v>0.183</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1198</v>
+        <v>0.7712</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3895</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1947</v>
+        <v>-4.0895</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.7526</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2857</v>
+        <v>1.3851</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5565</v>
+        <v>1.4647</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7292</v>
+        <v>-0.0796</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6621</v>
+        <v>-0.2958</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2795</v>
+        <v>-0.7137</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3826</v>
+        <v>0.4179</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8962</v>
+        <v>-0.7643</v>
       </c>
       <c r="E6" t="n">
-        <v>0.273</v>
+        <v>1.318</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1692</v>
+        <v>-2.0823</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2506</v>
+        <v>-0.4229</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5814</v>
+        <v>-0.3823</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3308</v>
+        <v>-0.0405</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7584</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6774</v>
+        <v>0.136</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5078</v>
+        <v>-1.2157</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.096</v>
+        <v>-0.5184</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4118</v>
+        <v>-0.6973</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3679</v>
+        <v>0.4296</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4882</v>
+        <v>0.5252</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8561</v>
+        <v>-0.0955</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.7447</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.7447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2387</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1218</v>
+        <v>0.1733</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3605</v>
+        <v>-1.0579</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4229</v>
+        <v>0.2506</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3823</v>
+        <v>0.5814</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0405</v>
+        <v>-0.3308</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7584</v>
       </c>
       <c r="K7" t="n">
-        <v>0.136</v>
+        <v>0.6774</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2157</v>
+        <v>-0.5078</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5184</v>
+        <v>-0.096</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6973</v>
+        <v>-0.4118</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9737</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q7" t="n">
+        <v>-0.9737</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1947</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-0.3562</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.7448</v>
+      </c>
+      <c r="V7" t="n">
         <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.9737</v>
-      </c>
-      <c r="S7" t="n">
-        <v>-1.0447</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.671</v>
-      </c>
-      <c r="U7" t="n">
-        <v>-0.3738</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-1.7447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5455</v>
+        <v>-2.6218</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2106</v>
+        <v>-0.5269</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3349</v>
+        <v>-2.0949</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.2867</v>
+        <v>-2.9524</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.4196</v>
+        <v>0.0626</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8671</v>
+        <v>-3.015</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.8896</v>
+        <v>-1.5249</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.8657</v>
+        <v>0.3875</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0238</v>
+        <v>-1.9125</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3972</v>
+        <v>-1.4275</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5538</v>
+        <v>-0.3249</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8433</v>
+        <v>-1.1026</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.1421</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1421</v>
+        <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8159999999999999</v>
+        <v>-0.952</v>
       </c>
       <c r="T8" t="n">
-        <v>1.4306</v>
+        <v>-0.192</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6146</v>
+        <v>-0.76</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9253</v>
+        <v>1.8668</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3905</v>
+        <v>3.3321</v>
       </c>
       <c r="X8" t="n">
         <v>-1.4653</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. PEDROSA BELLES</t>
+          <t>M. SAINZ DE LA MAZA GARRASTACHU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5682</v>
+        <v>-3.0299</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1747</v>
+        <v>-1.7228</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3935</v>
+        <v>-1.3071</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.205</v>
+        <v>-4.2867</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-3.4196</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6974</v>
+        <v>-0.8671</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8498</v>
+        <v>-2.8896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1437</v>
+        <v>-2.8657</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.9935</v>
+        <v>-0.0238</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3551</v>
+        <v>-1.3972</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6513</v>
+        <v>-0.5538</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7039</v>
+        <v>-0.8433</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7789</v>
+        <v>2.1421</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5316</v>
+        <v>0.3316</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3249</v>
+        <v>0.9183</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2068</v>
+        <v>-0.5868</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6105</v>
+        <v>0.9253</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3905</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6105</v>
+        <v>-1.4653</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>I. PEDROSA BELLES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6974</v>
+        <v>-3.1833</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3243</v>
+        <v>-1.7898</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3732</v>
+        <v>-1.3935</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9524</v>
+        <v>-3.205</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0626</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.015</v>
+        <v>-2.6974</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5249</v>
+        <v>-1.8498</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3875</v>
+        <v>0.1437</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9125</v>
+        <v>-1.9935</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4275</v>
+        <v>-1.3551</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3249</v>
+        <v>-0.6513</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1026</v>
+        <v>-0.7039</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5842000000000001</v>
+        <v>0.7789</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1421</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0277</v>
+        <v>-0.1467</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9893999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0383</v>
+        <v>-0.2068</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8668</v>
+        <v>-0.6105</v>
       </c>
       <c r="W10" t="n">
-        <v>3.3321</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4653</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.4704</v>
+        <v>-9.110200000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5489</v>
+        <v>-7.1608</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9215</v>
+        <v>-1.9493</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0098</v>
@@ -1312,13 +1312,13 @@
         <v>1.1684</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3894</v>
+        <v>-0.2503</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.2686</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4911</v>
+        <v>-0.5189</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8763</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.4031</v>
+        <v>-11.4758</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.419700000000001</v>
+        <v>-4.491999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.9837</v>
+        <v>-6.9836</v>
       </c>
       <c r="G12" t="n">
         <v>-9.5261</v>
@@ -1363,7 +1363,7 @@
         <v>-5.48</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9947999999999992</v>
+        <v>-0.9948000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-0.4941999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>11.6841</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7105999999999995</v>
+        <v>0.2171000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3503</v>
+        <v>4.2779</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.0611</v>
+        <v>-4.0609</v>
       </c>
       <c r="V12" t="n">
         <v>1.728499999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0291</v>
+        <v>6.0458</v>
       </c>
       <c r="E13" t="n">
-        <v>5.2978</v>
+        <v>4.0798</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7313</v>
+        <v>1.966</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4824</v>
+        <v>2.4393</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7321</v>
+        <v>1.6317</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7503</v>
+        <v>0.8076</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8283</v>
+        <v>1.7996</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2478</v>
+        <v>1.2316</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5805</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3459</v>
+        <v>0.6397</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4843</v>
+        <v>0.4001</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8302</v>
+        <v>0.2396</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9737</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9474</v>
+        <v>1.7526</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7631</v>
+        <v>-0.1724</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5464</v>
+        <v>-0.0461</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2168</v>
+        <v>-0.1262</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1901</v>
+        <v>3.9736</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.1032</v>
+        <v>4.2737</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.087</v>
+        <v>-0.3001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3867</v>
+        <v>4.7387</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5814</v>
+        <v>3.9024</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8052</v>
+        <v>0.8364</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4393</v>
+        <v>3.4824</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6317</v>
+        <v>2.7321</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8076</v>
+        <v>0.7503</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7996</v>
+        <v>3.8283</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2316</v>
+        <v>2.2478</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5679999999999999</v>
+        <v>1.5805</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6397</v>
+        <v>-0.3459</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4001</v>
+        <v>0.4843</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2396</v>
+        <v>-0.8302</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9474</v>
+        <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7526</v>
+        <v>1.9474</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8315</v>
+        <v>1.4728</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5445</v>
+        <v>1.1509</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.287</v>
+        <v>0.3218</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9736</v>
+        <v>-1.1901</v>
       </c>
       <c r="W14" t="n">
-        <v>4.2737</v>
+        <v>-0.1032</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3001</v>
+        <v>-1.087</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1633</v>
+        <v>4.0196</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8882</v>
+        <v>2.6888</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2751</v>
+        <v>1.3308</v>
       </c>
       <c r="G15" t="n">
         <v>1.2473</v>
@@ -1624,13 +1624,13 @@
         <v>2.921</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9056</v>
+        <v>0.7619</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2174</v>
+        <v>1.018</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3118</v>
+        <v>-0.2561</v>
       </c>
       <c r="V15" t="n">
         <v>-0.9106</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7628</v>
+        <v>3.883</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5417</v>
+        <v>5.4775</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2211</v>
+        <v>-1.5945</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1906</v>
+        <v>3.4447</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7514</v>
+        <v>1.6174</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4392</v>
+        <v>1.8273</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2984</v>
+        <v>3.4643</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2579</v>
+        <v>1.0726</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0405</v>
+        <v>2.3917</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1078</v>
+        <v>-0.0196</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5065</v>
+        <v>0.5448</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3987</v>
+        <v>-0.5644</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7789</v>
+        <v>1.5579</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7789</v>
+        <v>1.5579</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3522</v>
+        <v>-0.6105</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9054</v>
+        <v>-0.0978</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5532</v>
+        <v>-0.5127</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5091</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6621</v>
+        <v>2.1111</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1032</v>
+        <v>-2.6201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5864</v>
+        <v>2.4314</v>
       </c>
       <c r="E17" t="n">
-        <v>4.4808</v>
+        <v>2.0433</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8943</v>
+        <v>0.388</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4447</v>
+        <v>2.1906</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6174</v>
+        <v>1.7514</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8273</v>
+        <v>0.4392</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4643</v>
+        <v>2.2984</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0726</v>
+        <v>2.2579</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3917</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0196</v>
+        <v>-0.1078</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5448</v>
+        <v>-0.5065</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5644</v>
+        <v>0.3987</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.9071</v>
+        <v>0.0208</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0946</v>
+        <v>0.407</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8126</v>
+        <v>-0.3862</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5091</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1111</v>
+        <v>-0.6621</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6201</v>
+        <v>0.1032</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3667</v>
+        <v>-0.6595</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1399</v>
+        <v>-0.9373</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.2778</v>
       </c>
       <c r="G18" t="n">
         <v>0.1006</v>
@@ -1858,13 +1858,13 @@
         <v>0.7789</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1035</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7028</v>
+        <v>0.9054</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.3311</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9205</v>
+        <v>-0.7668</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6043</v>
+        <v>-1.3053</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6838</v>
+        <v>0.5385</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4556</v>
@@ -1936,13 +1936,13 @@
         <v>1.5579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6211</v>
+        <v>-0.4675</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3064</v>
+        <v>-0.0074</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3147</v>
+        <v>-0.4601</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4016</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3628</v>
+        <v>-1.8412</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.4373</v>
+        <v>-3.1383</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0745</v>
+        <v>1.2971</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1029</v>
@@ -2014,13 +2014,13 @@
         <v>2.1421</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4173</v>
+        <v>0.1043</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1883</v>
+        <v>0.4873</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6056</v>
+        <v>-0.383</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0637</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4235</v>
+        <v>-2.0932</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1621</v>
+        <v>-3.5656</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2614</v>
+        <v>1.4724</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.1437</v>
+        <v>-0.6764</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5132</v>
+        <v>-1.599</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6304999999999999</v>
+        <v>0.9226</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2346</v>
+        <v>-1.2212</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6106</v>
+        <v>-1.2135</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.624</v>
+        <v>-0.0077</v>
       </c>
       <c r="M21" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.5448</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0974</v>
+        <v>-0.3855</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0066</v>
+        <v>0.9303</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9737</v>
+        <v>-2.921</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3895</v>
+        <v>1.7526</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5255</v>
+        <v>-0.0704</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0462</v>
+        <v>0.2972</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4794</v>
+        <v>-0.3676</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2211</v>
+        <v>-0.178</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2211</v>
+        <v>-0.4575</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.185</v>
+        <v>-2.6901</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4627</v>
+        <v>-2.2618</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2777</v>
+        <v>-0.4283</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6764</v>
+        <v>-1.1437</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.599</v>
+        <v>-0.5132</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9226</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2212</v>
+        <v>-1.2346</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2135</v>
+        <v>-0.6106</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0077</v>
+        <v>-0.624</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5448</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3855</v>
+        <v>0.0974</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9303</v>
+        <v>-0.0066</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1684</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.921</v>
+        <v>-0.9737</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7526</v>
+        <v>0.3895</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1622</v>
+        <v>0.2589</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5999</v>
+        <v>-0.0535</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5623</v>
+        <v>0.3124</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.178</v>
+        <v>-1.2211</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4575</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.4032</v>
+        <v>13.0677</v>
       </c>
       <c r="E23" t="n">
-        <v>6.983599999999999</v>
+        <v>6.983499999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>5.4196</v>
+        <v>6.084199999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>9.526300000000001</v>
+        <v>9.526299999999999</v>
       </c>
       <c r="H23" t="n">
         <v>4.046099999999999</v>
@@ -2224,22 +2224,22 @@
         <v>8.531500000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>3.552000000000001</v>
+        <v>3.552</v>
       </c>
       <c r="L23" t="n">
-        <v>4.979500000000001</v>
+        <v>4.9795</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9946999999999999</v>
+        <v>0.9947</v>
       </c>
       <c r="N23" t="n">
         <v>0.4941</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5005999999999999</v>
+        <v>0.5005999999999998</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8948</v>
+        <v>3.894799999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.6842</v>
@@ -2248,13 +2248,13 @@
         <v>15.5788</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7107000000000001</v>
+        <v>1.3752</v>
       </c>
       <c r="T23" t="n">
-        <v>4.0611</v>
+        <v>4.061</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.3503</v>
+        <v>-2.6858</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7285</v>
